--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.491609150923559</v>
+        <v>1.542386487025078</v>
       </c>
       <c r="D2" t="n">
-        <v>9.580512822534612</v>
+        <v>1.556833333661874</v>
       </c>
       <c r="E2" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F2" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.627799258005035</v>
+        <v>0.5895173794258182</v>
       </c>
       <c r="D3" t="n">
-        <v>24.65836997361031</v>
+        <v>4.006985120711676</v>
       </c>
       <c r="E3" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F3" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.37835426693547</v>
+        <v>6.723982568377015</v>
       </c>
       <c r="D4" t="n">
-        <v>18.5431242817481</v>
+        <v>3.013257695784067</v>
       </c>
       <c r="E4" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F4" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.46400630133866</v>
+        <v>2.350401023967533</v>
       </c>
       <c r="D5" t="n">
-        <v>14.32983164595453</v>
+        <v>2.32859764246761</v>
       </c>
       <c r="E5" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F5" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.43436993510579</v>
+        <v>5.108085114454691</v>
       </c>
       <c r="D6" t="n">
-        <v>14.33621955408568</v>
+        <v>2.329635677538924</v>
       </c>
       <c r="E6" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F6" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.34175868336612</v>
+        <v>4.605535786046995</v>
       </c>
       <c r="D7" t="n">
-        <v>29.49168840139252</v>
+        <v>4.792399365226285</v>
       </c>
       <c r="E7" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F7" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.25392191177457</v>
+        <v>2.316262310663368</v>
       </c>
       <c r="D8" t="n">
-        <v>5.590169943749475</v>
+        <v>0.9084026158592896</v>
       </c>
       <c r="E8" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F8" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.187594044663745</v>
+        <v>0.8429840322578586</v>
       </c>
       <c r="D9" t="n">
-        <v>5.453374519468402</v>
+        <v>0.8861733594136153</v>
       </c>
       <c r="E9" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F9" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.07107485040054</v>
+        <v>7.161549663190089</v>
       </c>
       <c r="D10" t="n">
-        <v>43.20566179686372</v>
+        <v>7.020920041990355</v>
       </c>
       <c r="E10" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F10" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.14158982548453</v>
+        <v>3.598008346641236</v>
       </c>
       <c r="D11" t="n">
-        <v>17.06604816587601</v>
+        <v>2.773232826954852</v>
       </c>
       <c r="E11" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F11" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.35677317133491</v>
+        <v>6.232975640341922</v>
       </c>
       <c r="D12" t="n">
-        <v>38.42575435760594</v>
+        <v>6.244185083110965</v>
       </c>
       <c r="E12" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F12" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.820473059801982</v>
+        <v>1.433326872217822</v>
       </c>
       <c r="D13" t="n">
-        <v>20.65049494175252</v>
+        <v>3.355705428034784</v>
       </c>
       <c r="E13" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F13" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>20.85088896554405</v>
+        <v>3.388269456900909</v>
       </c>
       <c r="D14" t="n">
-        <v>21.08418202940381</v>
+        <v>3.42617957977812</v>
       </c>
       <c r="E14" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F14" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>14.10451668655915</v>
+        <v>2.291983961565862</v>
       </c>
       <c r="D15" t="n">
-        <v>37.26865137487015</v>
+        <v>6.0561558484164</v>
       </c>
       <c r="E15" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F15" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.552814253800456</v>
+        <v>1.552332316242574</v>
       </c>
       <c r="D16" t="n">
-        <v>9.808073808813118</v>
+        <v>1.593811993932132</v>
       </c>
       <c r="E16" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F16" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>15.96214825009464</v>
+        <v>2.59384909064038</v>
       </c>
       <c r="D17" t="n">
-        <v>15.89635964027195</v>
+        <v>2.583158441544192</v>
       </c>
       <c r="E17" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F17" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>5.351597610797578</v>
+        <v>0.8696346117546064</v>
       </c>
       <c r="D18" t="n">
-        <v>5.589487353293512</v>
+        <v>0.9082916949101957</v>
       </c>
       <c r="E18" t="n">
-        <v>12.67470768035953</v>
+        <v>2.059639998058423</v>
       </c>
       <c r="F18" t="n">
-        <v>11.41714839896571</v>
+        <v>1.855286614831928</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
